--- a/D-00001/operation-mapping_D-00001.xlsx
+++ b/D-00001/operation-mapping_D-00001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\D-00001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B91415F-4470-43EB-A94D-A31B7449DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4D4A2E-FB17-4929-B911-389DE7DC2295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t xml:space="preserve">API                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
   </si>
@@ -67,6 +67,21 @@
   </si>
   <si>
     <t>API UX UBAG Customer Offer API V1</t>
+  </si>
+  <si>
+    <t>API BS Servicing Order Bill Paid V1</t>
+  </si>
+  <si>
+    <t>BS</t>
+  </si>
+  <si>
+    <t>/servicing-orders/{id}/execute</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>Execute</t>
   </si>
 </sst>
 </file>
@@ -102,9 +117,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,8 +402,8 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.109375" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="49.33203125" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -439,7 +453,27 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/D-00001/operation-mapping_D-00001.xlsx
+++ b/D-00001/operation-mapping_D-00001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\D-00001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4D4A2E-FB17-4929-B911-389DE7DC2295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C414235-44AE-49EF-9DD9-B514823E2C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t xml:space="preserve">API                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>Execute</t>
+  </si>
+  <si>
+    <t>API BS Customer Credit Rating Paid V1</t>
+  </si>
+  <si>
+    <t>/customer-credit/{id}/internal-reporting</t>
   </si>
 </sst>
 </file>
@@ -399,11 +405,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" customWidth="1"/>
-    <col min="6" max="6" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -472,6 +478,29 @@
         <v>16</v>
       </c>
       <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
         <v>18</v>
       </c>
     </row>

--- a/D-00001/operation-mapping_D-00001.xlsx
+++ b/D-00001/operation-mapping_D-00001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\D-00001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C414235-44AE-49EF-9DD9-B514823E2C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C54991B-73BA-492F-9758-75CC307EF3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t xml:space="preserve">API                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
   </si>
@@ -88,6 +88,12 @@
   </si>
   <si>
     <t>/customer-credit/{id}/internal-reporting</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/customer-credit/{id}/order/initiate</t>
   </si>
 </sst>
 </file>
@@ -405,11 +411,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="49.33203125" customWidth="1"/>
-    <col min="6" max="6" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -501,6 +507,29 @@
         <v>20</v>
       </c>
       <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
         <v>18</v>
       </c>
     </row>
